--- a/ig/nr/rm-mes-id/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr/rm-mes-id/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T12:27:20+00:00</t>
+    <t>2023-03-31T12:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr/rm-mes-id/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
+++ b/ig/nr/rm-mes-id/StructureDefinition-mesures-fr-observation-bodyheight.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T12:33:59+00:00</t>
+    <t>2023-03-31T15:20:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
